--- a/apps/api/test/fixtures/delhivery-wallet-sample.xlsx
+++ b/apps/api/test/fixtures/delhivery-wallet-sample.xlsx
@@ -162,7 +162,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
+          <t xml:space="preserve">{"wbn": "AWB-REVISED", "zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -224,7 +224,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
+          <t xml:space="preserve">{"wbn": "AWB-REVISED", "zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -286,7 +286,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
+          <t xml:space="preserve">{"wbn": "AWB-BOTH", "zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -348,7 +348,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
+          <t xml:space="preserve">{"wbn": "AWB-BOTH", "zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -410,7 +410,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
+          <t xml:space="preserve">{"wbn": "AWB-ZERO", "zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
+          <t xml:space="preserve">{"wbn": "AWB-PLAIN", "zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
+          <t xml:space="preserve">{"wbn": "AWB-PLAIN", "zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
+          <t xml:space="preserve">{"wbn": "AWB-REVISED", "zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
+          <t xml:space="preserve">{"wbn": "AWB-ZERO", "zn": "B", "cgm": 320.0, "st": "Delivered"}</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
